--- a/inst/extdata/china_urban_population.xlsx
+++ b/inst/extdata/china_urban_population.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28000" windowHeight="14980"/>
+    <workbookView windowHeight="15520"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -9008,7 +9008,7 @@
         <v>183</v>
       </c>
       <c r="B513" s="2">
-        <v>469003</v>
+        <v>460400</v>
       </c>
       <c r="C513" s="2">
         <v>2020</v>
@@ -9022,7 +9022,7 @@
         <v>183</v>
       </c>
       <c r="B514" s="2">
-        <v>469003</v>
+        <v>460400</v>
       </c>
       <c r="C514" s="2">
         <v>2021</v>
@@ -9036,7 +9036,7 @@
         <v>183</v>
       </c>
       <c r="B515" s="2">
-        <v>469003</v>
+        <v>460400</v>
       </c>
       <c r="C515" s="2">
         <v>2022</v>
